--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127272108</v>
       </c>
       <c r="B2" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127270666</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127274223</v>
       </c>
       <c r="B4" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127270671</v>
       </c>
       <c r="B5" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91439</v>
+        <v>91445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97520</v>
+        <v>97526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127273876</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127271244</v>
       </c>
       <c r="B12" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>91343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R11" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91343</v>
+        <v>91325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R12" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127272108</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91445</v>
+        <v>91446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97526</v>
+        <v>97527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B11" t="n">
-        <v>91343</v>
+        <v>91326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R11" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B12" t="n">
-        <v>91325</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R12" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R2" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R3" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R11" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R12" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127270666</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127274223</v>
       </c>
       <c r="B4" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127270671</v>
       </c>
       <c r="B5" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91446</v>
+        <v>91450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97527</v>
+        <v>97531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R11" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R12" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R2" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R3" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R2" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R3" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R11" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R12" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R2" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R3" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>127274223</v>
       </c>
       <c r="B4" t="n">
-        <v>75147</v>
+        <v>75149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127270671</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91450</v>
+        <v>91452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97531</v>
+        <v>97533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R11" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R12" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R2" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R3" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R11" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R12" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R2" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B3" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R3" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>127274223</v>
       </c>
       <c r="B4" t="n">
-        <v>75149</v>
+        <v>75152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127270671</v>
       </c>
       <c r="B5" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91458</v>
+        <v>91461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97539</v>
+        <v>97542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B11" t="n">
-        <v>91356</v>
+        <v>91341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R11" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B12" t="n">
-        <v>91338</v>
+        <v>91359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R12" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R2" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R3" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>127274223</v>
       </c>
       <c r="B4" t="n">
-        <v>75152</v>
+        <v>75158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127270671</v>
       </c>
       <c r="B5" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91461</v>
+        <v>91469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97542</v>
+        <v>97550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B11" t="n">
-        <v>91341</v>
+        <v>91367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R11" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B12" t="n">
-        <v>91359</v>
+        <v>91349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R12" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 54140-2024 artfynd.xlsx
+++ b/artfynd/A 54140-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127270666</v>
+        <v>127272108</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454088</v>
+        <v>454176</v>
       </c>
       <c r="R2" t="n">
-        <v>7080851</v>
+        <v>7081093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127272108</v>
+        <v>127270666</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454176</v>
+        <v>454088</v>
       </c>
       <c r="R3" t="n">
-        <v>7081093</v>
+        <v>7080851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>127271520</v>
       </c>
       <c r="B6" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127273367</v>
       </c>
       <c r="B7" t="n">
-        <v>91469</v>
+        <v>91470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127273617</v>
       </c>
       <c r="B8" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127271787</v>
       </c>
       <c r="B9" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127273120</v>
       </c>
       <c r="B10" t="n">
-        <v>97550</v>
+        <v>97551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127271244</v>
+        <v>127273876</v>
       </c>
       <c r="B11" t="n">
-        <v>91367</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454163</v>
+        <v>454178</v>
       </c>
       <c r="R11" t="n">
-        <v>7080984</v>
+        <v>7080970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127273876</v>
+        <v>127271244</v>
       </c>
       <c r="B12" t="n">
-        <v>91349</v>
+        <v>91368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454178</v>
+        <v>454163</v>
       </c>
       <c r="R12" t="n">
-        <v>7080970</v>
+        <v>7080984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
